--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OREGON_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OREGON_2022.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C62">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C156">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C551">
